--- a/banks/W06_Kahoot匯入.xlsx
+++ b/banks/W06_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,22 +491,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>產物</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>酶原</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>受質</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>酶原</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>酵素</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>產物</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -526,19 +526,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>催化</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>受質</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>酵素</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>催化</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>輔酶</t>
@@ -549,7 +549,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -561,30 +561,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>產物</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>輔酶</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>催化</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>酶原</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>產物</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>催化</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -596,30 +596,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>過渡態</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>活性部位</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>維生素</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>過渡態</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>誘導契合</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>活性部位</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -636,25 +636,25 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>催化</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>受質</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>酵素</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>受質</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>催化</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>過渡態</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>專一性</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>過渡態</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>活性部位</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>活化能</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>活性部位</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -771,14 +771,14 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>誘導契合</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>過渡態</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>誘導契合</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>反應速率</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>過渡態</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>活化能</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>誘導契合</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>過渡態</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,30 +841,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>輔因子</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>輔基</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>輔酶</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>受質</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>輔因子</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>輔基</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>酵素</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>輔基</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>產物</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>輔酶</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>產物</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>酵素</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>輔基</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>輔因子</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>維生素</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>活化能</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>專一性</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>輔酶</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>輔基</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>酶原</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>活化能</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>酶原</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>輔基</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>輔酶</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,170 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>活化能</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>維生素</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>反應速率</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>活性部位</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>維生素</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:自由能反應進程圖) 標號1所指的雙箭頭代表什麼?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>過渡態</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>自由能變化(ΔG)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>受質</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>活化能</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:誘導契合圖) 圖中下排酵素彎曲並包住受質代表哪個概念?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>誘導契合</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>鎖與鑰匙</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>活性部位</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>誘導契合—酵素形狀改變去包住受質</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>輔基—跟酵素鬆散結合的維生素</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>活化能—反應完成後剩下的能量</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>酶原—已經啟動的酵素</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>為什麼胰蛋白酶不能拿來分解脂肪?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>脂肪不是分子不能被分解</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>胰蛋白酶已經變性</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>胰蛋白酶沒有活性部位</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>酵素有專一性活性部位只配合特定受質</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
